--- a/Packet Tracer/IP address.xlsx
+++ b/Packet Tracer/IP address.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\2025-2026\Vizsgaremek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C858492-8FD6-4B8A-B574-32CAF9C461BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D38C1A-1BAA-49CF-BDD6-16974F26DDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18000" windowHeight="9270" xr2:uid="{282A7FAF-A36E-4327-A1FC-20DFE78AAB8B}"/>
+    <workbookView xWindow="4560" yWindow="1650" windowWidth="18000" windowHeight="9270" xr2:uid="{282A7FAF-A36E-4327-A1FC-20DFE78AAB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Szegmensek:</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Eszközök:</t>
   </si>
   <si>
-    <t>Ip cím</t>
-  </si>
-  <si>
     <t>HQ LAN</t>
   </si>
   <si>
@@ -79,13 +76,43 @@
   </si>
   <si>
     <t>192.168.50.0 /25</t>
+  </si>
+  <si>
+    <t>PC-k, Laptopok, ASA, Switch, HomeRouter</t>
+  </si>
+  <si>
+    <t>HomeRouter + Wi-Fi eszközök</t>
+  </si>
+  <si>
+    <t>Szerverek, PC-k</t>
+  </si>
+  <si>
+    <t>HQ Router, HR Router, Servers Router, WAN Switch, Server</t>
+  </si>
+  <si>
+    <t>Ip cím példa</t>
+  </si>
+  <si>
+    <t>ASA: 10.0.0.1</t>
+  </si>
+  <si>
+    <t>HomeRouter: 192.168.10.1</t>
+  </si>
+  <si>
+    <t>HomeRouter: 192.168.20.1</t>
+  </si>
+  <si>
+    <t>Server: 192.168.30.10</t>
+  </si>
+  <si>
+    <t>HQ Router: 192.168.50.1HR Router: 192.168.50.2Servers Router: 192.168.50.3Server: 192.168.50.10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,16 +121,77 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC00CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF66FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF119F4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0D5CB3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -111,18 +199,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0D5CB3"/>
+      <color rgb="FF0C70B4"/>
+      <color rgb="FF119F4A"/>
+      <color rgb="FF1C9444"/>
+      <color rgb="FFFF66FF"/>
+      <color rgb="FFCC00CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -436,70 +570,110 @@
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="3" max="3" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="94.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" s="12" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
+      <c r="C6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentum" ma:contentTypeID="0x01010023F5B51375CA5F48927837B7C846372A" ma:contentTypeVersion="9" ma:contentTypeDescription="Új dokumentum létrehozása." ma:contentTypeScope="" ma:versionID="8569a69c5601f6c1bb879d16883b0958">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5d86d87e-4eda-498c-af70-6f2a616ddbb6" xmlns:ns4="04042892-774f-4e1e-9f29-f5d0072c223e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a67e81d8575ab49cd545615425cd976b" ns3:_="" ns4:_="">
     <xsd:import namespace="5d86d87e-4eda-498c-af70-6f2a616ddbb6"/>
@@ -694,15 +868,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -712,6 +877,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4803927-6207-4FE4-B061-1837ED41B397}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{892E8834-8248-4024-B715-C322DC7266E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -730,14 +903,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4803927-6207-4FE4-B061-1837ED41B397}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B4D7FF0-86FE-421D-8413-60F43A915104}">
   <ds:schemaRefs>
